--- a/output_tunning/tabel_tuning_tcn_bigru.xlsx
+++ b/output_tunning/tabel_tuning_tcn_bigru.xlsx
@@ -496,13 +496,13 @@
         <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.1051</v>
+        <v>1.0829</v>
       </c>
       <c r="J2" t="n">
-        <v>18.45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -532,27 +532,27 @@
         <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>32</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.2345</v>
+        <v>1.0593</v>
       </c>
       <c r="J3" t="n">
-        <v>24.7</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="4">
@@ -568,13 +568,13 @@
         <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>32</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1.1238</v>
+        <v>1.154</v>
       </c>
       <c r="J4" t="n">
-        <v>13.37</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="5">
@@ -604,27 +604,27 @@
         <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>32</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1.2013</v>
+        <v>1.1144</v>
       </c>
       <c r="J5" t="n">
-        <v>23.09</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="6">
@@ -640,13 +640,13 @@
         <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>32</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -654,13 +654,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1.2291</v>
+        <v>1.0849</v>
       </c>
       <c r="J6" t="n">
-        <v>13.77</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -676,27 +676,27 @@
         <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2.7817</v>
+        <v>1.0745</v>
       </c>
       <c r="J7" t="n">
-        <v>8.81</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="8">
@@ -712,13 +712,13 @@
         <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1.1048</v>
+        <v>1.1774</v>
       </c>
       <c r="J8" t="n">
-        <v>18</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="9">
@@ -748,27 +748,27 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>32</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1.762</v>
+        <v>1.4375</v>
       </c>
       <c r="J9" t="n">
-        <v>11.64</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="10">
@@ -784,13 +784,13 @@
         <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1.1936</v>
+        <v>1.0806</v>
       </c>
       <c r="J10" t="n">
-        <v>17.75</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="11">
@@ -820,27 +820,27 @@
         <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1.1042</v>
+        <v>1.0888</v>
       </c>
       <c r="J11" t="n">
-        <v>26.58</v>
+        <v>26.98</v>
       </c>
     </row>
     <row r="12">
@@ -856,13 +856,13 @@
         <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1.7299</v>
+        <v>1.1589</v>
       </c>
       <c r="J12" t="n">
-        <v>16.44</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="13">
@@ -892,27 +892,27 @@
         <v>32</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>64</v>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1.2437</v>
+        <v>1.0845</v>
       </c>
       <c r="J13" t="n">
-        <v>28.24</v>
+        <v>20.28</v>
       </c>
     </row>
     <row r="14">
@@ -928,13 +928,13 @@
         <v>32</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>64</v>
       </c>
       <c r="F14" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1.2301</v>
+        <v>1.0923</v>
       </c>
       <c r="J14" t="n">
-        <v>12.99</v>
+        <v>27.67</v>
       </c>
     </row>
     <row r="15">
@@ -964,27 +964,27 @@
         <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>64</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1.232</v>
+        <v>1.1566</v>
       </c>
       <c r="J15" t="n">
-        <v>28.39</v>
+        <v>20.96</v>
       </c>
     </row>
     <row r="16">
@@ -1000,13 +1000,13 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>64</v>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.3407</v>
+        <v>1.1523</v>
       </c>
       <c r="J16" t="n">
-        <v>12.95</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="17">
@@ -1036,27 +1036,27 @@
         <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>64</v>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.1402</v>
+        <v>1.4117</v>
       </c>
       <c r="J17" t="n">
-        <v>28.51</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="18">
@@ -1072,13 +1072,13 @@
         <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
         <v>32</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1.1491</v>
+        <v>1.1435</v>
       </c>
       <c r="J18" t="n">
-        <v>16.81</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="19">
@@ -1108,27 +1108,27 @@
         <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>32</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1.1317</v>
+        <v>1.2875</v>
       </c>
       <c r="J19" t="n">
-        <v>26.51</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="20">
@@ -1144,13 +1144,13 @@
         <v>32</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
         <v>32</v>
       </c>
       <c r="F20" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1.0678</v>
+        <v>1.0807</v>
       </c>
       <c r="J20" t="n">
-        <v>20.64</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="21">
@@ -1180,27 +1180,27 @@
         <v>32</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
         <v>32</v>
       </c>
       <c r="F21" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1.1294</v>
+        <v>1.2464</v>
       </c>
       <c r="J21" t="n">
-        <v>25.88</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="22">
@@ -1216,13 +1216,13 @@
         <v>32</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
         <v>32</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1.5334</v>
+        <v>1.0875</v>
       </c>
       <c r="J22" t="n">
-        <v>17.48</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="23">
@@ -1252,27 +1252,27 @@
         <v>32</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
         <v>32</v>
       </c>
       <c r="F23" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1.0908</v>
+        <v>1.075</v>
       </c>
       <c r="J23" t="n">
-        <v>35.42</v>
+        <v>23.35</v>
       </c>
     </row>
     <row r="24">
@@ -1288,13 +1288,13 @@
         <v>32</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
         <v>32</v>
       </c>
       <c r="F24" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1302,13 +1302,13 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1.1934</v>
+        <v>1.1207</v>
       </c>
       <c r="J24" t="n">
-        <v>15.45</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="25">
@@ -1324,27 +1324,27 @@
         <v>32</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
         <v>32</v>
       </c>
       <c r="F25" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1.2876</v>
+        <v>1.5863</v>
       </c>
       <c r="J25" t="n">
-        <v>27.22</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="26">
@@ -1360,13 +1360,13 @@
         <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
         <v>64</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1374,13 +1374,13 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1.1824</v>
+        <v>1.0733</v>
       </c>
       <c r="J26" t="n">
-        <v>28.92</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="27">
@@ -1396,27 +1396,27 @@
         <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
         <v>64</v>
       </c>
       <c r="F27" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1.1574</v>
+        <v>1.3939</v>
       </c>
       <c r="J27" t="n">
-        <v>43.62</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="28">
@@ -1432,13 +1432,13 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
         <v>64</v>
       </c>
       <c r="F28" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1446,13 +1446,13 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1.1241</v>
+        <v>1.131</v>
       </c>
       <c r="J28" t="n">
-        <v>20.63</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="29">
@@ -1468,27 +1468,27 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>64</v>
       </c>
       <c r="F29" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1.0625</v>
+        <v>1.1525</v>
       </c>
       <c r="J29" t="n">
-        <v>32.09</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="30">
@@ -1504,13 +1504,13 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
         <v>64</v>
       </c>
       <c r="F30" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1518,13 +1518,13 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1.1115</v>
+        <v>1.1558</v>
       </c>
       <c r="J30" t="n">
-        <v>24.31</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="31">
@@ -1540,27 +1540,27 @@
         <v>32</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
         <v>64</v>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1.1262</v>
+        <v>1.1006</v>
       </c>
       <c r="J31" t="n">
-        <v>43.22</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="32">
@@ -1576,13 +1576,13 @@
         <v>32</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>64</v>
       </c>
       <c r="F32" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1.1229</v>
+        <v>1.0735</v>
       </c>
       <c r="J32" t="n">
-        <v>26.69</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="33">
@@ -1612,27 +1612,27 @@
         <v>32</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
         <v>64</v>
       </c>
       <c r="F33" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1.4639</v>
+        <v>1.1709</v>
       </c>
       <c r="J33" t="n">
-        <v>20.56</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="34">
@@ -1648,13 +1648,13 @@
         <v>64</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
         <v>32</v>
       </c>
       <c r="F34" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1662,13 +1662,13 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1.1652</v>
+        <v>1.2301</v>
       </c>
       <c r="J34" t="n">
-        <v>28.64</v>
+        <v>24.51</v>
       </c>
     </row>
     <row r="35">
@@ -1684,27 +1684,27 @@
         <v>64</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>32</v>
       </c>
       <c r="F35" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1.2375</v>
+        <v>1.1584</v>
       </c>
       <c r="J35" t="n">
-        <v>28.18</v>
+        <v>25.37</v>
       </c>
     </row>
     <row r="36">
@@ -1720,13 +1720,13 @@
         <v>64</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>32</v>
       </c>
       <c r="F36" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1734,13 +1734,13 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1.0729</v>
+        <v>1.1085</v>
       </c>
       <c r="J36" t="n">
-        <v>14.77</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="37">
@@ -1756,27 +1756,27 @@
         <v>64</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>32</v>
       </c>
       <c r="F37" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1.1724</v>
+        <v>1.1382</v>
       </c>
       <c r="J37" t="n">
-        <v>26.7</v>
+        <v>25.11</v>
       </c>
     </row>
     <row r="38">
@@ -1792,13 +1792,13 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
         <v>32</v>
       </c>
       <c r="F38" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1806,13 +1806,13 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1.1257</v>
+        <v>1.1167</v>
       </c>
       <c r="J38" t="n">
-        <v>15.09</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="39">
@@ -1828,27 +1828,27 @@
         <v>64</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
         <v>32</v>
       </c>
       <c r="F39" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1.1297</v>
+        <v>1.3046</v>
       </c>
       <c r="J39" t="n">
-        <v>39.7</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="40">
@@ -1864,13 +1864,13 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
         <v>32</v>
       </c>
       <c r="F40" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1878,13 +1878,13 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1.0788</v>
+        <v>1.4709</v>
       </c>
       <c r="J40" t="n">
-        <v>17.99</v>
+        <v>24.88</v>
       </c>
     </row>
     <row r="41">
@@ -1900,27 +1900,27 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>32</v>
       </c>
       <c r="F41" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1.0889</v>
+        <v>1.1212</v>
       </c>
       <c r="J41" t="n">
-        <v>26.77</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="42">
@@ -1936,13 +1936,13 @@
         <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
         <v>64</v>
       </c>
       <c r="F42" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1950,13 +1950,13 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1.0744</v>
+        <v>1.1193</v>
       </c>
       <c r="J42" t="n">
-        <v>22.52</v>
+        <v>40.29</v>
       </c>
     </row>
     <row r="43">
@@ -1972,27 +1972,27 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
         <v>64</v>
       </c>
       <c r="F43" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1.0989</v>
+        <v>1.2007</v>
       </c>
       <c r="J43" t="n">
-        <v>30.85</v>
+        <v>29.52</v>
       </c>
     </row>
     <row r="44">
@@ -2008,13 +2008,13 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
         <v>64</v>
       </c>
       <c r="F44" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1.0818</v>
+        <v>1.1312</v>
       </c>
       <c r="J44" t="n">
-        <v>21.96</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="45">
@@ -2044,27 +2044,27 @@
         <v>64</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
         <v>64</v>
       </c>
       <c r="F45" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1.0764</v>
+        <v>1.1508</v>
       </c>
       <c r="J45" t="n">
-        <v>32.53</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="46">
@@ -2080,13 +2080,13 @@
         <v>64</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
         <v>64</v>
       </c>
       <c r="F46" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1.1037</v>
+        <v>1.4813</v>
       </c>
       <c r="J46" t="n">
-        <v>17.6</v>
+        <v>17.63</v>
       </c>
     </row>
     <row r="47">
@@ -2116,27 +2116,27 @@
         <v>64</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
         <v>64</v>
       </c>
       <c r="F47" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1.0715</v>
+        <v>1.3723</v>
       </c>
       <c r="J47" t="n">
-        <v>34.88</v>
+        <v>30.17</v>
       </c>
     </row>
     <row r="48">
@@ -2152,13 +2152,13 @@
         <v>64</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
         <v>64</v>
       </c>
       <c r="F48" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2166,13 +2166,13 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1.2055</v>
+        <v>1.0717</v>
       </c>
       <c r="J48" t="n">
-        <v>15.05</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="49">
@@ -2188,27 +2188,27 @@
         <v>64</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
         <v>64</v>
       </c>
       <c r="F49" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1.088</v>
+        <v>1.1202</v>
       </c>
       <c r="J49" t="n">
-        <v>30.98</v>
+        <v>17.96</v>
       </c>
     </row>
     <row r="50">
@@ -2224,13 +2224,13 @@
         <v>64</v>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
         <v>32</v>
       </c>
       <c r="F50" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2238,13 +2238,13 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1.0989</v>
+        <v>1.2006</v>
       </c>
       <c r="J50" t="n">
-        <v>32.74</v>
+        <v>37.25</v>
       </c>
     </row>
     <row r="51">
@@ -2260,27 +2260,27 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
         <v>32</v>
       </c>
       <c r="F51" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1.1999</v>
+        <v>1.3593</v>
       </c>
       <c r="J51" t="n">
-        <v>34.13</v>
+        <v>29.93</v>
       </c>
     </row>
     <row r="52">
@@ -2296,13 +2296,13 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
         <v>32</v>
       </c>
       <c r="F52" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2310,13 +2310,13 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1.1326</v>
+        <v>1.5785</v>
       </c>
       <c r="J52" t="n">
-        <v>25.11</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="53">
@@ -2332,27 +2332,27 @@
         <v>64</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
         <v>32</v>
       </c>
       <c r="F53" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1.1568</v>
+        <v>1.1022</v>
       </c>
       <c r="J53" t="n">
-        <v>23.37</v>
+        <v>27.62</v>
       </c>
     </row>
     <row r="54">
@@ -2368,13 +2368,13 @@
         <v>64</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
         <v>32</v>
       </c>
       <c r="F54" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1.1659</v>
+        <v>1.1207</v>
       </c>
       <c r="J54" t="n">
-        <v>20.69</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="55">
@@ -2404,27 +2404,27 @@
         <v>64</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
         <v>32</v>
       </c>
       <c r="F55" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1.1295</v>
+        <v>1.6808</v>
       </c>
       <c r="J55" t="n">
-        <v>43.01</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="56">
@@ -2440,13 +2440,13 @@
         <v>64</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
         <v>32</v>
       </c>
       <c r="F56" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2454,13 +2454,13 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1.0883</v>
+        <v>1.2551</v>
       </c>
       <c r="J56" t="n">
-        <v>19.96</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="57">
@@ -2476,27 +2476,27 @@
         <v>64</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
         <v>32</v>
       </c>
       <c r="F57" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1.2078</v>
+        <v>1.1411</v>
       </c>
       <c r="J57" t="n">
-        <v>23.06</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="58">
@@ -2512,13 +2512,13 @@
         <v>64</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
         <v>64</v>
       </c>
       <c r="F58" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1.1416</v>
+        <v>1.6913</v>
       </c>
       <c r="J58" t="n">
-        <v>29.21</v>
+        <v>18.38</v>
       </c>
     </row>
     <row r="59">
@@ -2548,27 +2548,27 @@
         <v>64</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
         <v>64</v>
       </c>
       <c r="F59" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1.1782</v>
+        <v>1.1187</v>
       </c>
       <c r="J59" t="n">
-        <v>29.27</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="60">
@@ -2584,13 +2584,13 @@
         <v>64</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
         <v>64</v>
       </c>
       <c r="F60" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2598,13 +2598,13 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1.1289</v>
+        <v>1.1272</v>
       </c>
       <c r="J60" t="n">
-        <v>19.4</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="61">
@@ -2620,27 +2620,27 @@
         <v>64</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
         <v>64</v>
       </c>
       <c r="F61" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1.0729</v>
+        <v>1.1282</v>
       </c>
       <c r="J61" t="n">
-        <v>36.66</v>
+        <v>28.81</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>64</v>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
         <v>64</v>
       </c>
       <c r="F62" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1.1511</v>
+        <v>1.8165</v>
       </c>
       <c r="J62" t="n">
-        <v>29.01</v>
+        <v>19.85</v>
       </c>
     </row>
     <row r="63">
@@ -2692,27 +2692,27 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
         <v>64</v>
       </c>
       <c r="F63" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1.1411</v>
+        <v>1.0565</v>
       </c>
       <c r="J63" t="n">
-        <v>32.92</v>
+        <v>42.88</v>
       </c>
     </row>
     <row r="64">
@@ -2728,13 +2728,13 @@
         <v>64</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
         <v>64</v>
       </c>
       <c r="F64" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2745,10 +2745,10 @@
         <v>12</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1.6543</v>
+        <v>1.1163</v>
       </c>
       <c r="J64" t="n">
-        <v>16.74</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="65">
@@ -2764,27 +2764,27 @@
         <v>64</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
         <v>64</v>
       </c>
       <c r="F65" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1.1345</v>
+        <v>1.1438</v>
       </c>
       <c r="J65" t="n">
-        <v>39.02</v>
+        <v>30.72</v>
       </c>
     </row>
     <row r="66">
@@ -2800,13 +2800,13 @@
         <v>32</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
         <v>32</v>
       </c>
       <c r="F66" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2814,13 +2814,13 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1.249</v>
+        <v>1.393</v>
       </c>
       <c r="J66" t="n">
-        <v>19.99</v>
+        <v>25.65</v>
       </c>
     </row>
     <row r="67">
@@ -2836,27 +2836,27 @@
         <v>32</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
         <v>32</v>
       </c>
       <c r="F67" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1.4454</v>
+        <v>1.3918</v>
       </c>
       <c r="J67" t="n">
-        <v>32.53</v>
+        <v>19.09</v>
       </c>
     </row>
     <row r="68">
@@ -2872,13 +2872,13 @@
         <v>32</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
         <v>32</v>
       </c>
       <c r="F68" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2886,13 +2886,13 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1.3346</v>
+        <v>1.2717</v>
       </c>
       <c r="J68" t="n">
-        <v>17.27</v>
+        <v>18.03</v>
       </c>
     </row>
     <row r="69">
@@ -2908,27 +2908,27 @@
         <v>32</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
         <v>32</v>
       </c>
       <c r="F69" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1.2422</v>
+        <v>1.2832</v>
       </c>
       <c r="J69" t="n">
-        <v>28.16</v>
+        <v>16.54</v>
       </c>
     </row>
     <row r="70">
@@ -2944,13 +2944,13 @@
         <v>32</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
         <v>32</v>
       </c>
       <c r="F70" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2958,13 +2958,13 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1.3056</v>
+        <v>2.5556</v>
       </c>
       <c r="J70" t="n">
-        <v>17.97</v>
+        <v>35.36</v>
       </c>
     </row>
     <row r="71">
@@ -2980,27 +2980,27 @@
         <v>32</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
         <v>32</v>
       </c>
       <c r="F71" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1.2598</v>
+        <v>1.6696</v>
       </c>
       <c r="J71" t="n">
-        <v>25.64</v>
+        <v>28.81</v>
       </c>
     </row>
     <row r="72">
@@ -3016,13 +3016,13 @@
         <v>32</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
         <v>32</v>
       </c>
       <c r="F72" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3030,13 +3030,13 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1.359</v>
+        <v>1.7465</v>
       </c>
       <c r="J72" t="n">
-        <v>14.34</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="73">
@@ -3052,27 +3052,27 @@
         <v>32</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
         <v>32</v>
       </c>
       <c r="F73" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1.2522</v>
+        <v>2.1073</v>
       </c>
       <c r="J73" t="n">
-        <v>29.19</v>
+        <v>11.84</v>
       </c>
     </row>
     <row r="74">
@@ -3088,13 +3088,13 @@
         <v>32</v>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
         <v>64</v>
       </c>
       <c r="F74" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3102,13 +3102,13 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1.291</v>
+        <v>1.2421</v>
       </c>
       <c r="J74" t="n">
-        <v>33.78</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="75">
@@ -3124,27 +3124,27 @@
         <v>32</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
         <v>64</v>
       </c>
       <c r="F75" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1.5422</v>
+        <v>1.2178</v>
       </c>
       <c r="J75" t="n">
-        <v>26.51</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="76">
@@ -3160,13 +3160,13 @@
         <v>32</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
         <v>64</v>
       </c>
       <c r="F76" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3174,13 +3174,13 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1.2066</v>
+        <v>2.0009</v>
       </c>
       <c r="J76" t="n">
-        <v>17.12</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="77">
@@ -3196,27 +3196,27 @@
         <v>32</v>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
         <v>64</v>
       </c>
       <c r="F77" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1.2654</v>
+        <v>1.7795</v>
       </c>
       <c r="J77" t="n">
-        <v>32.91</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="78">
@@ -3232,13 +3232,13 @@
         <v>32</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
         <v>64</v>
       </c>
       <c r="F78" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3246,13 +3246,13 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1.4976</v>
+        <v>1.4282</v>
       </c>
       <c r="J78" t="n">
-        <v>22.93</v>
+        <v>28.76</v>
       </c>
     </row>
     <row r="79">
@@ -3268,27 +3268,27 @@
         <v>32</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
         <v>64</v>
       </c>
       <c r="F79" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1.831</v>
+        <v>1.2656</v>
       </c>
       <c r="J79" t="n">
-        <v>28.7</v>
+        <v>33.09</v>
       </c>
     </row>
     <row r="80">
@@ -3304,13 +3304,13 @@
         <v>32</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
         <v>64</v>
       </c>
       <c r="F80" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1.1758</v>
+        <v>1.3847</v>
       </c>
       <c r="J80" t="n">
-        <v>21.96</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="81">
@@ -3340,27 +3340,27 @@
         <v>32</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
         <v>64</v>
       </c>
       <c r="F81" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1.3637</v>
+        <v>1.3139</v>
       </c>
       <c r="J81" t="n">
-        <v>18.52</v>
+        <v>25.97</v>
       </c>
     </row>
     <row r="82">
@@ -3376,13 +3376,13 @@
         <v>32</v>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
         <v>32</v>
       </c>
       <c r="F82" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1.3003</v>
+        <v>1.4704</v>
       </c>
       <c r="J82" t="n">
-        <v>26.53</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="83">
@@ -3412,27 +3412,27 @@
         <v>32</v>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
         <v>32</v>
       </c>
       <c r="F83" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1.1889</v>
+        <v>1.26</v>
       </c>
       <c r="J83" t="n">
-        <v>42.76</v>
+        <v>26.03</v>
       </c>
     </row>
     <row r="84">
@@ -3448,13 +3448,13 @@
         <v>32</v>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
         <v>32</v>
       </c>
       <c r="F84" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3462,13 +3462,13 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1.3208</v>
+        <v>1.2983</v>
       </c>
       <c r="J84" t="n">
-        <v>16.14</v>
+        <v>19.59</v>
       </c>
     </row>
     <row r="85">
@@ -3484,27 +3484,27 @@
         <v>32</v>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
         <v>32</v>
       </c>
       <c r="F85" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1.513</v>
+        <v>1.3115</v>
       </c>
       <c r="J85" t="n">
-        <v>27.81</v>
+        <v>25.35</v>
       </c>
     </row>
     <row r="86">
@@ -3520,13 +3520,13 @@
         <v>32</v>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E86" t="n">
         <v>32</v>
       </c>
       <c r="F86" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1.476</v>
+        <v>1.4941</v>
       </c>
       <c r="J86" t="n">
-        <v>14.82</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="87">
@@ -3556,27 +3556,27 @@
         <v>32</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
         <v>32</v>
       </c>
       <c r="F87" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1.2389</v>
+        <v>1.809</v>
       </c>
       <c r="J87" t="n">
-        <v>39.53</v>
+        <v>37.98</v>
       </c>
     </row>
     <row r="88">
@@ -3592,13 +3592,13 @@
         <v>32</v>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
         <v>32</v>
       </c>
       <c r="F88" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3606,13 +3606,13 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1.3146</v>
+        <v>1.2516</v>
       </c>
       <c r="J88" t="n">
-        <v>21.62</v>
+        <v>24.62</v>
       </c>
     </row>
     <row r="89">
@@ -3628,27 +3628,27 @@
         <v>32</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
         <v>32</v>
       </c>
       <c r="F89" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1.5489</v>
+        <v>1.2075</v>
       </c>
       <c r="J89" t="n">
-        <v>22.4</v>
+        <v>25.54</v>
       </c>
     </row>
     <row r="90">
@@ -3664,13 +3664,13 @@
         <v>32</v>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
         <v>64</v>
       </c>
       <c r="F90" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3678,13 +3678,13 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1.2078</v>
+        <v>1.2433</v>
       </c>
       <c r="J90" t="n">
-        <v>29.77</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="91">
@@ -3700,27 +3700,27 @@
         <v>32</v>
       </c>
       <c r="D91" t="n">
+        <v>3</v>
+      </c>
+      <c r="E91" t="n">
+        <v>64</v>
+      </c>
+      <c r="F91" t="n">
+        <v>8</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0.0015</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
         <v>5</v>
       </c>
-      <c r="E91" t="n">
-        <v>64</v>
-      </c>
-      <c r="F91" t="n">
-        <v>16</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>0.0001</t>
-        </is>
-      </c>
-      <c r="H91" t="n">
-        <v>37</v>
-      </c>
       <c r="I91" s="2" t="n">
-        <v>1.2194</v>
+        <v>1.516</v>
       </c>
       <c r="J91" t="n">
-        <v>39.07</v>
+        <v>22.14</v>
       </c>
     </row>
     <row r="92">
@@ -3736,13 +3736,13 @@
         <v>32</v>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
         <v>64</v>
       </c>
       <c r="F92" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1.265</v>
+        <v>1.4692</v>
       </c>
       <c r="J92" t="n">
-        <v>17.76</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="93">
@@ -3772,27 +3772,27 @@
         <v>32</v>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
         <v>64</v>
       </c>
       <c r="F93" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1.2143</v>
+        <v>1.2888</v>
       </c>
       <c r="J93" t="n">
-        <v>34.75</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="94">
@@ -3808,13 +3808,13 @@
         <v>32</v>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E94" t="n">
         <v>64</v>
       </c>
       <c r="F94" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3822,13 +3822,13 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1.1977</v>
+        <v>1.2932</v>
       </c>
       <c r="J94" t="n">
-        <v>25.82</v>
+        <v>41.56</v>
       </c>
     </row>
     <row r="95">
@@ -3844,27 +3844,27 @@
         <v>32</v>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E95" t="n">
         <v>64</v>
       </c>
       <c r="F95" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1.2683</v>
+        <v>1.3547</v>
       </c>
       <c r="J95" t="n">
-        <v>28.89</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="96">
@@ -3880,13 +3880,13 @@
         <v>32</v>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E96" t="n">
         <v>64</v>
       </c>
       <c r="F96" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1.9898</v>
+        <v>1.4484</v>
       </c>
       <c r="J96" t="n">
-        <v>20.94</v>
+        <v>22.13</v>
       </c>
     </row>
     <row r="97">
@@ -3916,27 +3916,27 @@
         <v>32</v>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E97" t="n">
         <v>64</v>
       </c>
       <c r="F97" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1.3639</v>
+        <v>1.2179</v>
       </c>
       <c r="J97" t="n">
-        <v>22.83</v>
+        <v>27.22</v>
       </c>
     </row>
     <row r="98">
@@ -3952,13 +3952,13 @@
         <v>64</v>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
         <v>32</v>
       </c>
       <c r="F98" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3966,13 +3966,13 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1.214</v>
+        <v>1.5343</v>
       </c>
       <c r="J98" t="n">
-        <v>32.35</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="99">
@@ -3988,27 +3988,27 @@
         <v>64</v>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
         <v>32</v>
       </c>
       <c r="F99" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1.27</v>
+        <v>1.2497</v>
       </c>
       <c r="J99" t="n">
-        <v>41.21</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="100">
@@ -4024,13 +4024,13 @@
         <v>64</v>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
         <v>32</v>
       </c>
       <c r="F100" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4038,13 +4038,13 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1.274</v>
+        <v>1.3162</v>
       </c>
       <c r="J100" t="n">
-        <v>20.3</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="101">
@@ -4060,27 +4060,27 @@
         <v>64</v>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
         <v>32</v>
       </c>
       <c r="F101" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>1.321</v>
+        <v>1.3584</v>
       </c>
       <c r="J101" t="n">
-        <v>32.35</v>
+        <v>18.94</v>
       </c>
     </row>
     <row r="102">
@@ -4096,13 +4096,13 @@
         <v>64</v>
       </c>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
         <v>32</v>
       </c>
       <c r="F102" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>1.692</v>
+        <v>1.5056</v>
       </c>
       <c r="J102" t="n">
-        <v>24.37</v>
+        <v>24.87</v>
       </c>
     </row>
     <row r="103">
@@ -4132,27 +4132,27 @@
         <v>64</v>
       </c>
       <c r="D103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E103" t="n">
         <v>32</v>
       </c>
       <c r="F103" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>1.2286</v>
+        <v>1.5384</v>
       </c>
       <c r="J103" t="n">
-        <v>47.82</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="104">
@@ -4168,13 +4168,13 @@
         <v>64</v>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
         <v>32</v>
       </c>
       <c r="F104" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4182,13 +4182,13 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1.1788</v>
+        <v>1.5325</v>
       </c>
       <c r="J104" t="n">
-        <v>18.39</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="105">
@@ -4204,27 +4204,27 @@
         <v>64</v>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
         <v>32</v>
       </c>
       <c r="F105" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>1.2533</v>
+        <v>1.4428</v>
       </c>
       <c r="J105" t="n">
-        <v>33.35</v>
+        <v>31.18</v>
       </c>
     </row>
     <row r="106">
@@ -4240,13 +4240,13 @@
         <v>64</v>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
         <v>64</v>
       </c>
       <c r="F106" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4254,13 +4254,13 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1.1922</v>
+        <v>1.418</v>
       </c>
       <c r="J106" t="n">
-        <v>27.4</v>
+        <v>49.13</v>
       </c>
     </row>
     <row r="107">
@@ -4276,27 +4276,27 @@
         <v>64</v>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
         <v>64</v>
       </c>
       <c r="F107" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>1.1743</v>
+        <v>1.4193</v>
       </c>
       <c r="J107" t="n">
-        <v>54.54</v>
+        <v>26.97</v>
       </c>
     </row>
     <row r="108">
@@ -4312,13 +4312,13 @@
         <v>64</v>
       </c>
       <c r="D108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
         <v>64</v>
       </c>
       <c r="F108" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4326,13 +4326,13 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1.2453</v>
+        <v>1.4286</v>
       </c>
       <c r="J108" t="n">
-        <v>22.91</v>
+        <v>24.85</v>
       </c>
     </row>
     <row r="109">
@@ -4348,27 +4348,27 @@
         <v>64</v>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
         <v>64</v>
       </c>
       <c r="F109" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1.204</v>
+        <v>1.369</v>
       </c>
       <c r="J109" t="n">
-        <v>36.24</v>
+        <v>33.08</v>
       </c>
     </row>
     <row r="110">
@@ -4384,13 +4384,13 @@
         <v>64</v>
       </c>
       <c r="D110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E110" t="n">
         <v>64</v>
       </c>
       <c r="F110" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1.2073</v>
+        <v>1.2731</v>
       </c>
       <c r="J110" t="n">
-        <v>40.78</v>
+        <v>38.04</v>
       </c>
     </row>
     <row r="111">
@@ -4420,27 +4420,27 @@
         <v>64</v>
       </c>
       <c r="D111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E111" t="n">
         <v>64</v>
       </c>
       <c r="F111" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>2.0608</v>
+        <v>1.2524</v>
       </c>
       <c r="J111" t="n">
-        <v>22.33</v>
+        <v>46.77</v>
       </c>
     </row>
     <row r="112">
@@ -4456,13 +4456,13 @@
         <v>64</v>
       </c>
       <c r="D112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E112" t="n">
         <v>64</v>
       </c>
       <c r="F112" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4470,13 +4470,13 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>1.8374</v>
+        <v>1.2193</v>
       </c>
       <c r="J112" t="n">
-        <v>18.25</v>
+        <v>31.06</v>
       </c>
     </row>
     <row r="113">
@@ -4492,27 +4492,27 @@
         <v>64</v>
       </c>
       <c r="D113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E113" t="n">
         <v>64</v>
       </c>
       <c r="F113" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1.2545</v>
+        <v>1.4827</v>
       </c>
       <c r="J113" t="n">
-        <v>37.72</v>
+        <v>34.19</v>
       </c>
     </row>
     <row r="114">
@@ -4528,13 +4528,13 @@
         <v>64</v>
       </c>
       <c r="D114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E114" t="n">
         <v>32</v>
       </c>
       <c r="F114" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4542,13 +4542,13 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>1.1947</v>
+        <v>1.234</v>
       </c>
       <c r="J114" t="n">
-        <v>33.33</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="115">
@@ -4564,27 +4564,27 @@
         <v>64</v>
       </c>
       <c r="D115" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E115" t="n">
         <v>32</v>
       </c>
       <c r="F115" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1.2298</v>
+        <v>1.2774</v>
       </c>
       <c r="J115" t="n">
-        <v>41.48</v>
+        <v>43.15</v>
       </c>
     </row>
     <row r="116">
@@ -4600,13 +4600,13 @@
         <v>64</v>
       </c>
       <c r="D116" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E116" t="n">
         <v>32</v>
       </c>
       <c r="F116" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4614,13 +4614,13 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>1.2458</v>
+        <v>1.5035</v>
       </c>
       <c r="J116" t="n">
-        <v>23.46</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="117">
@@ -4636,27 +4636,27 @@
         <v>64</v>
       </c>
       <c r="D117" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E117" t="n">
         <v>32</v>
       </c>
       <c r="F117" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>1.185</v>
+        <v>1.309</v>
       </c>
       <c r="J117" t="n">
-        <v>36.98</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="118">
@@ -4672,13 +4672,13 @@
         <v>64</v>
       </c>
       <c r="D118" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E118" t="n">
         <v>32</v>
       </c>
       <c r="F118" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>1.5731</v>
+        <v>1.3904</v>
       </c>
       <c r="J118" t="n">
-        <v>17.98</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="119">
@@ -4708,27 +4708,27 @@
         <v>64</v>
       </c>
       <c r="D119" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E119" t="n">
         <v>32</v>
       </c>
       <c r="F119" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>1.2691</v>
+        <v>1.3872</v>
       </c>
       <c r="J119" t="n">
-        <v>53.87</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="120">
@@ -4744,13 +4744,13 @@
         <v>64</v>
       </c>
       <c r="D120" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E120" t="n">
         <v>32</v>
       </c>
       <c r="F120" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4758,13 +4758,13 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>1.2705</v>
+        <v>1.1823</v>
       </c>
       <c r="J120" t="n">
-        <v>30.31</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="121">
@@ -4780,27 +4780,27 @@
         <v>64</v>
       </c>
       <c r="D121" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E121" t="n">
         <v>32</v>
       </c>
       <c r="F121" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>1.2497</v>
+        <v>1.2691</v>
       </c>
       <c r="J121" t="n">
-        <v>39.54</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="122">
@@ -4816,13 +4816,13 @@
         <v>64</v>
       </c>
       <c r="D122" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E122" t="n">
         <v>64</v>
       </c>
       <c r="F122" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -4830,13 +4830,13 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>1.3576</v>
+        <v>1.2979</v>
       </c>
       <c r="J122" t="n">
-        <v>28.91</v>
+        <v>27.63</v>
       </c>
     </row>
     <row r="123">
@@ -4852,27 +4852,27 @@
         <v>64</v>
       </c>
       <c r="D123" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E123" t="n">
         <v>64</v>
       </c>
       <c r="F123" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>1.2328</v>
+        <v>1.3652</v>
       </c>
       <c r="J123" t="n">
-        <v>61.29</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="124">
@@ -4888,13 +4888,13 @@
         <v>64</v>
       </c>
       <c r="D124" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E124" t="n">
         <v>64</v>
       </c>
       <c r="F124" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -4902,13 +4902,13 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>1.2043</v>
+        <v>1.266</v>
       </c>
       <c r="J124" t="n">
-        <v>37.77</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="125">
@@ -4924,27 +4924,27 @@
         <v>64</v>
       </c>
       <c r="D125" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E125" t="n">
         <v>64</v>
       </c>
       <c r="F125" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>1.1791</v>
+        <v>1.2685</v>
       </c>
       <c r="J125" t="n">
-        <v>40.55</v>
+        <v>27.19</v>
       </c>
     </row>
     <row r="126">
@@ -4960,13 +4960,13 @@
         <v>64</v>
       </c>
       <c r="D126" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E126" t="n">
         <v>64</v>
       </c>
       <c r="F126" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -4974,13 +4974,13 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>1.6407</v>
+        <v>1.264</v>
       </c>
       <c r="J126" t="n">
-        <v>23.83</v>
+        <v>51.81</v>
       </c>
     </row>
     <row r="127">
@@ -4996,27 +4996,27 @@
         <v>64</v>
       </c>
       <c r="D127" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E127" t="n">
         <v>64</v>
       </c>
       <c r="F127" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>1.2041</v>
+        <v>1.1946</v>
       </c>
       <c r="J127" t="n">
-        <v>65.48999999999999</v>
+        <v>45.13</v>
       </c>
     </row>
     <row r="128">
@@ -5032,13 +5032,13 @@
         <v>64</v>
       </c>
       <c r="D128" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E128" t="n">
         <v>64</v>
       </c>
       <c r="F128" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -5046,13 +5046,13 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>1.3077</v>
+        <v>1.2323</v>
       </c>
       <c r="J128" t="n">
-        <v>21.43</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="129">
@@ -5068,27 +5068,27 @@
         <v>64</v>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E129" t="n">
         <v>64</v>
       </c>
       <c r="F129" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>1.2418</v>
+        <v>1.2061</v>
       </c>
       <c r="J129" t="n">
-        <v>44.61</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="130">
@@ -5104,13 +5104,13 @@
         <v>32</v>
       </c>
       <c r="D130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E130" t="n">
         <v>32</v>
       </c>
       <c r="F130" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>1.5322</v>
+        <v>2.1959</v>
       </c>
       <c r="J130" t="n">
-        <v>21.23</v>
+        <v>27.77</v>
       </c>
     </row>
     <row r="131">
@@ -5140,27 +5140,27 @@
         <v>32</v>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E131" t="n">
         <v>32</v>
       </c>
       <c r="F131" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>1.976</v>
+        <v>1.3677</v>
       </c>
       <c r="J131" t="n">
-        <v>18.22</v>
+        <v>28.87</v>
       </c>
     </row>
     <row r="132">
@@ -5176,13 +5176,13 @@
         <v>32</v>
       </c>
       <c r="D132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E132" t="n">
         <v>32</v>
       </c>
       <c r="F132" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -5190,13 +5190,13 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>1.402</v>
+        <v>1.552</v>
       </c>
       <c r="J132" t="n">
-        <v>17.82</v>
+        <v>20.71</v>
       </c>
     </row>
     <row r="133">
@@ -5212,27 +5212,27 @@
         <v>32</v>
       </c>
       <c r="D133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E133" t="n">
         <v>32</v>
       </c>
       <c r="F133" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>1.6742</v>
+        <v>1.4066</v>
       </c>
       <c r="J133" t="n">
-        <v>32.17</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="134">
@@ -5248,13 +5248,13 @@
         <v>32</v>
       </c>
       <c r="D134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E134" t="n">
         <v>32</v>
       </c>
       <c r="F134" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -5262,13 +5262,13 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>1.9293</v>
+        <v>3.297</v>
       </c>
       <c r="J134" t="n">
-        <v>24.22</v>
+        <v>25.76</v>
       </c>
     </row>
     <row r="135">
@@ -5284,27 +5284,27 @@
         <v>32</v>
       </c>
       <c r="D135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E135" t="n">
         <v>32</v>
       </c>
       <c r="F135" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>1.357</v>
+        <v>1.4001</v>
       </c>
       <c r="J135" t="n">
-        <v>44.93</v>
+        <v>23.83</v>
       </c>
     </row>
     <row r="136">
@@ -5320,13 +5320,13 @@
         <v>32</v>
       </c>
       <c r="D136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E136" t="n">
         <v>32</v>
       </c>
       <c r="F136" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -5334,13 +5334,13 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>1.4402</v>
+        <v>1.9458</v>
       </c>
       <c r="J136" t="n">
-        <v>14.23</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="137">
@@ -5356,27 +5356,27 @@
         <v>32</v>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E137" t="n">
         <v>32</v>
       </c>
       <c r="F137" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>2.3563</v>
+        <v>1.4343</v>
       </c>
       <c r="J137" t="n">
-        <v>19.37</v>
+        <v>18.36</v>
       </c>
     </row>
     <row r="138">
@@ -5392,13 +5392,13 @@
         <v>32</v>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E138" t="n">
         <v>64</v>
       </c>
       <c r="F138" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -5406,13 +5406,13 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>1.4964</v>
+        <v>1.5864</v>
       </c>
       <c r="J138" t="n">
-        <v>20.06</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="139">
@@ -5428,27 +5428,27 @@
         <v>32</v>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E139" t="n">
         <v>64</v>
       </c>
       <c r="F139" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>1.4014</v>
+        <v>1.8159</v>
       </c>
       <c r="J139" t="n">
-        <v>27.31</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="140">
@@ -5464,13 +5464,13 @@
         <v>32</v>
       </c>
       <c r="D140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E140" t="n">
         <v>64</v>
       </c>
       <c r="F140" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -5478,13 +5478,13 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>1.333</v>
+        <v>1.3732</v>
       </c>
       <c r="J140" t="n">
-        <v>21.19</v>
+        <v>24.71</v>
       </c>
     </row>
     <row r="141">
@@ -5500,27 +5500,27 @@
         <v>32</v>
       </c>
       <c r="D141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E141" t="n">
         <v>64</v>
       </c>
       <c r="F141" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>1.6243</v>
+        <v>1.3202</v>
       </c>
       <c r="J141" t="n">
-        <v>28.64</v>
+        <v>31.02</v>
       </c>
     </row>
     <row r="142">
@@ -5536,13 +5536,13 @@
         <v>32</v>
       </c>
       <c r="D142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E142" t="n">
         <v>64</v>
       </c>
       <c r="F142" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -5550,13 +5550,13 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>1.524</v>
+        <v>1.3993</v>
       </c>
       <c r="J142" t="n">
-        <v>19.84</v>
+        <v>26.38</v>
       </c>
     </row>
     <row r="143">
@@ -5572,27 +5572,27 @@
         <v>32</v>
       </c>
       <c r="D143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E143" t="n">
         <v>64</v>
       </c>
       <c r="F143" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1.4091</v>
+        <v>2.4553</v>
       </c>
       <c r="J143" t="n">
-        <v>34.24</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="144">
@@ -5608,13 +5608,13 @@
         <v>32</v>
       </c>
       <c r="D144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E144" t="n">
         <v>64</v>
       </c>
       <c r="F144" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -5622,13 +5622,13 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>1.5381</v>
+        <v>1.9401</v>
       </c>
       <c r="J144" t="n">
-        <v>17.96</v>
+        <v>26.42</v>
       </c>
     </row>
     <row r="145">
@@ -5644,27 +5644,27 @@
         <v>32</v>
       </c>
       <c r="D145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E145" t="n">
         <v>64</v>
       </c>
       <c r="F145" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1.5029</v>
+        <v>1.7818</v>
       </c>
       <c r="J145" t="n">
-        <v>30.36</v>
+        <v>18.56</v>
       </c>
     </row>
     <row r="146">
@@ -5680,13 +5680,13 @@
         <v>32</v>
       </c>
       <c r="D146" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E146" t="n">
         <v>32</v>
       </c>
       <c r="F146" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -5694,13 +5694,13 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>1.3389</v>
+        <v>1.5715</v>
       </c>
       <c r="J146" t="n">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="147">
@@ -5716,27 +5716,27 @@
         <v>32</v>
       </c>
       <c r="D147" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E147" t="n">
         <v>32</v>
       </c>
       <c r="F147" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>1.3224</v>
+        <v>1.543</v>
       </c>
       <c r="J147" t="n">
-        <v>41.56</v>
+        <v>26.53</v>
       </c>
     </row>
     <row r="148">
@@ -5752,13 +5752,13 @@
         <v>32</v>
       </c>
       <c r="D148" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E148" t="n">
         <v>32</v>
       </c>
       <c r="F148" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -5766,13 +5766,13 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>1.5116</v>
+        <v>1.3849</v>
       </c>
       <c r="J148" t="n">
-        <v>22.45</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="149">
@@ -5788,27 +5788,27 @@
         <v>32</v>
       </c>
       <c r="D149" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E149" t="n">
         <v>32</v>
       </c>
       <c r="F149" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>1.727</v>
+        <v>1.4107</v>
       </c>
       <c r="J149" t="n">
-        <v>35</v>
+        <v>19.18</v>
       </c>
     </row>
     <row r="150">
@@ -5824,13 +5824,13 @@
         <v>32</v>
       </c>
       <c r="D150" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E150" t="n">
         <v>32</v>
       </c>
       <c r="F150" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -5841,10 +5841,10 @@
         <v>10</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>1.5711</v>
+        <v>1.8542</v>
       </c>
       <c r="J150" t="n">
-        <v>20.89</v>
+        <v>26.76</v>
       </c>
     </row>
     <row r="151">
@@ -5860,27 +5860,27 @@
         <v>32</v>
       </c>
       <c r="D151" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E151" t="n">
         <v>32</v>
       </c>
       <c r="F151" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>1.3601</v>
+        <v>1.6808</v>
       </c>
       <c r="J151" t="n">
-        <v>40.31</v>
+        <v>18.57</v>
       </c>
     </row>
     <row r="152">
@@ -5896,13 +5896,13 @@
         <v>32</v>
       </c>
       <c r="D152" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E152" t="n">
         <v>32</v>
       </c>
       <c r="F152" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -5910,13 +5910,13 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>1.8121</v>
+        <v>2.1811</v>
       </c>
       <c r="J152" t="n">
-        <v>16.13</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="153">
@@ -5932,27 +5932,27 @@
         <v>32</v>
       </c>
       <c r="D153" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E153" t="n">
         <v>32</v>
       </c>
       <c r="F153" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1.4441</v>
+        <v>1.9964</v>
       </c>
       <c r="J153" t="n">
-        <v>27.1</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="154">
@@ -5968,13 +5968,13 @@
         <v>32</v>
       </c>
       <c r="D154" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E154" t="n">
         <v>64</v>
       </c>
       <c r="F154" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -5982,13 +5982,13 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>1.3686</v>
+        <v>1.5509</v>
       </c>
       <c r="J154" t="n">
-        <v>24.34</v>
+        <v>22.65</v>
       </c>
     </row>
     <row r="155">
@@ -6004,27 +6004,27 @@
         <v>32</v>
       </c>
       <c r="D155" t="n">
+        <v>3</v>
+      </c>
+      <c r="E155" t="n">
+        <v>64</v>
+      </c>
+      <c r="F155" t="n">
+        <v>8</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>0.0015</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
         <v>5</v>
       </c>
-      <c r="E155" t="n">
-        <v>64</v>
-      </c>
-      <c r="F155" t="n">
-        <v>16</v>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>0.0001</t>
-        </is>
-      </c>
-      <c r="H155" t="n">
-        <v>7</v>
-      </c>
       <c r="I155" s="2" t="n">
-        <v>2.6707</v>
+        <v>1.6726</v>
       </c>
       <c r="J155" t="n">
-        <v>21.76</v>
+        <v>25.48</v>
       </c>
     </row>
     <row r="156">
@@ -6040,13 +6040,13 @@
         <v>32</v>
       </c>
       <c r="D156" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E156" t="n">
         <v>64</v>
       </c>
       <c r="F156" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -6054,13 +6054,13 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>1.3411</v>
+        <v>1.437</v>
       </c>
       <c r="J156" t="n">
-        <v>21.38</v>
+        <v>22.36</v>
       </c>
     </row>
     <row r="157">
@@ -6076,27 +6076,27 @@
         <v>32</v>
       </c>
       <c r="D157" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E157" t="n">
         <v>64</v>
       </c>
       <c r="F157" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1.4338</v>
+        <v>1.3304</v>
       </c>
       <c r="J157" t="n">
-        <v>37.71</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="158">
@@ -6112,13 +6112,13 @@
         <v>32</v>
       </c>
       <c r="D158" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E158" t="n">
         <v>64</v>
       </c>
       <c r="F158" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -6126,13 +6126,13 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>1.3972</v>
+        <v>1.328</v>
       </c>
       <c r="J158" t="n">
-        <v>26.74</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="159">
@@ -6148,27 +6148,27 @@
         <v>32</v>
       </c>
       <c r="D159" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E159" t="n">
         <v>64</v>
       </c>
       <c r="F159" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>1.9095</v>
+        <v>2.19</v>
       </c>
       <c r="J159" t="n">
-        <v>27.55</v>
+        <v>20.77</v>
       </c>
     </row>
     <row r="160">
@@ -6184,13 +6184,13 @@
         <v>32</v>
       </c>
       <c r="D160" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E160" t="n">
         <v>64</v>
       </c>
       <c r="F160" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -6198,13 +6198,13 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>1.5572</v>
+        <v>1.4164</v>
       </c>
       <c r="J160" t="n">
-        <v>23.46</v>
+        <v>20.68</v>
       </c>
     </row>
     <row r="161">
@@ -6220,27 +6220,27 @@
         <v>32</v>
       </c>
       <c r="D161" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E161" t="n">
         <v>64</v>
       </c>
       <c r="F161" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>2.0317</v>
+        <v>1.414</v>
       </c>
       <c r="J161" t="n">
-        <v>33.88</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="162">
@@ -6256,13 +6256,13 @@
         <v>64</v>
       </c>
       <c r="D162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E162" t="n">
         <v>32</v>
       </c>
       <c r="F162" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -6270,13 +6270,13 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>1.5735</v>
+        <v>1.6026</v>
       </c>
       <c r="J162" t="n">
-        <v>23.35</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="163">
@@ -6292,27 +6292,27 @@
         <v>64</v>
       </c>
       <c r="D163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E163" t="n">
         <v>32</v>
       </c>
       <c r="F163" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>1.3725</v>
+        <v>1.4646</v>
       </c>
       <c r="J163" t="n">
-        <v>55.33</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="164">
@@ -6328,13 +6328,13 @@
         <v>64</v>
       </c>
       <c r="D164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E164" t="n">
         <v>32</v>
       </c>
       <c r="F164" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -6342,13 +6342,13 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>1.8063</v>
+        <v>1.539</v>
       </c>
       <c r="J164" t="n">
-        <v>18.64</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="165">
@@ -6364,27 +6364,27 @@
         <v>64</v>
       </c>
       <c r="D165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E165" t="n">
         <v>32</v>
       </c>
       <c r="F165" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H165" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>1.5308</v>
+        <v>1.8691</v>
       </c>
       <c r="J165" t="n">
-        <v>38.7</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="166">
@@ -6400,13 +6400,13 @@
         <v>64</v>
       </c>
       <c r="D166" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E166" t="n">
         <v>32</v>
       </c>
       <c r="F166" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -6414,13 +6414,13 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>1.8157</v>
+        <v>2.2558</v>
       </c>
       <c r="J166" t="n">
-        <v>21.22</v>
+        <v>30.94</v>
       </c>
     </row>
     <row r="167">
@@ -6436,27 +6436,27 @@
         <v>64</v>
       </c>
       <c r="D167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E167" t="n">
         <v>32</v>
       </c>
       <c r="F167" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1.6491</v>
+        <v>1.7738</v>
       </c>
       <c r="J167" t="n">
-        <v>36.94</v>
+        <v>70.83</v>
       </c>
     </row>
     <row r="168">
@@ -6472,13 +6472,13 @@
         <v>64</v>
       </c>
       <c r="D168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E168" t="n">
         <v>32</v>
       </c>
       <c r="F168" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>1.4891</v>
+        <v>1.8523</v>
       </c>
       <c r="J168" t="n">
-        <v>17.26</v>
+        <v>23.27</v>
       </c>
     </row>
     <row r="169">
@@ -6508,27 +6508,27 @@
         <v>64</v>
       </c>
       <c r="D169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E169" t="n">
         <v>32</v>
       </c>
       <c r="F169" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>1.3722</v>
+        <v>1.7016</v>
       </c>
       <c r="J169" t="n">
-        <v>32.06</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="170">
@@ -6544,13 +6544,13 @@
         <v>64</v>
       </c>
       <c r="D170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E170" t="n">
         <v>64</v>
       </c>
       <c r="F170" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -6558,13 +6558,13 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>1.4333</v>
+        <v>1.3924</v>
       </c>
       <c r="J170" t="n">
-        <v>25.98</v>
+        <v>48.34</v>
       </c>
     </row>
     <row r="171">
@@ -6580,27 +6580,27 @@
         <v>64</v>
       </c>
       <c r="D171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E171" t="n">
         <v>64</v>
       </c>
       <c r="F171" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>1.4185</v>
+        <v>1.4027</v>
       </c>
       <c r="J171" t="n">
-        <v>36.51</v>
+        <v>30.44</v>
       </c>
     </row>
     <row r="172">
@@ -6616,13 +6616,13 @@
         <v>64</v>
       </c>
       <c r="D172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E172" t="n">
         <v>64</v>
       </c>
       <c r="F172" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -6630,13 +6630,13 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>1.3831</v>
+        <v>1.6435</v>
       </c>
       <c r="J172" t="n">
-        <v>29.28</v>
+        <v>28.47</v>
       </c>
     </row>
     <row r="173">
@@ -6652,27 +6652,27 @@
         <v>64</v>
       </c>
       <c r="D173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E173" t="n">
         <v>64</v>
       </c>
       <c r="F173" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>1.3757</v>
+        <v>1.4586</v>
       </c>
       <c r="J173" t="n">
-        <v>44.56</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="174">
@@ -6688,13 +6688,13 @@
         <v>64</v>
       </c>
       <c r="D174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E174" t="n">
         <v>64</v>
       </c>
       <c r="F174" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -6702,13 +6702,13 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>1.3814</v>
+        <v>1.5354</v>
       </c>
       <c r="J174" t="n">
-        <v>29.5</v>
+        <v>27.93</v>
       </c>
     </row>
     <row r="175">
@@ -6724,27 +6724,27 @@
         <v>64</v>
       </c>
       <c r="D175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E175" t="n">
         <v>64</v>
       </c>
       <c r="F175" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H175" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>1.3686</v>
+        <v>1.377</v>
       </c>
       <c r="J175" t="n">
-        <v>40.07</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="176">
@@ -6760,13 +6760,13 @@
         <v>64</v>
       </c>
       <c r="D176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E176" t="n">
         <v>64</v>
       </c>
       <c r="F176" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -6774,13 +6774,13 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>1.3901</v>
+        <v>1.459</v>
       </c>
       <c r="J176" t="n">
-        <v>20.84</v>
+        <v>24.91</v>
       </c>
     </row>
     <row r="177">
@@ -6796,27 +6796,27 @@
         <v>64</v>
       </c>
       <c r="D177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E177" t="n">
         <v>64</v>
       </c>
       <c r="F177" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H177" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>1.8921</v>
+        <v>1.6663</v>
       </c>
       <c r="J177" t="n">
-        <v>25.64</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="178">
@@ -6832,13 +6832,13 @@
         <v>64</v>
       </c>
       <c r="D178" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E178" t="n">
         <v>32</v>
       </c>
       <c r="F178" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -6846,13 +6846,13 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>1.3861</v>
+        <v>1.5207</v>
       </c>
       <c r="J178" t="n">
-        <v>22.38</v>
+        <v>39.48</v>
       </c>
     </row>
     <row r="179">
@@ -6868,27 +6868,27 @@
         <v>64</v>
       </c>
       <c r="D179" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E179" t="n">
         <v>32</v>
       </c>
       <c r="F179" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H179" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>1.4038</v>
+        <v>1.5183</v>
       </c>
       <c r="J179" t="n">
-        <v>36.16</v>
+        <v>32.23</v>
       </c>
     </row>
     <row r="180">
@@ -6904,13 +6904,13 @@
         <v>64</v>
       </c>
       <c r="D180" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E180" t="n">
         <v>32</v>
       </c>
       <c r="F180" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -6918,13 +6918,13 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>1.3644</v>
+        <v>1.4487</v>
       </c>
       <c r="J180" t="n">
-        <v>29.24</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="181">
@@ -6940,27 +6940,27 @@
         <v>64</v>
       </c>
       <c r="D181" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E181" t="n">
         <v>32</v>
       </c>
       <c r="F181" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H181" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>1.4214</v>
+        <v>1.4402</v>
       </c>
       <c r="J181" t="n">
-        <v>41.72</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="182">
@@ -6976,13 +6976,13 @@
         <v>64</v>
       </c>
       <c r="D182" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E182" t="n">
         <v>32</v>
       </c>
       <c r="F182" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>2.5615</v>
+        <v>1.4495</v>
       </c>
       <c r="J182" t="n">
-        <v>24.76</v>
+        <v>43.02</v>
       </c>
     </row>
     <row r="183">
@@ -7012,27 +7012,27 @@
         <v>64</v>
       </c>
       <c r="D183" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E183" t="n">
         <v>32</v>
       </c>
       <c r="F183" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H183" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>1.8061</v>
+        <v>1.546</v>
       </c>
       <c r="J183" t="n">
-        <v>41.87</v>
+        <v>33.46</v>
       </c>
     </row>
     <row r="184">
@@ -7048,13 +7048,13 @@
         <v>64</v>
       </c>
       <c r="D184" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E184" t="n">
         <v>32</v>
       </c>
       <c r="F184" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -7062,13 +7062,13 @@
         </is>
       </c>
       <c r="H184" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>1.4968</v>
+        <v>1.5203</v>
       </c>
       <c r="J184" t="n">
-        <v>26.14</v>
+        <v>26.59</v>
       </c>
     </row>
     <row r="185">
@@ -7084,27 +7084,27 @@
         <v>64</v>
       </c>
       <c r="D185" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E185" t="n">
         <v>32</v>
       </c>
       <c r="F185" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H185" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>1.394</v>
+        <v>1.6394</v>
       </c>
       <c r="J185" t="n">
-        <v>45.08</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="186">
@@ -7120,13 +7120,13 @@
         <v>64</v>
       </c>
       <c r="D186" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E186" t="n">
         <v>64</v>
       </c>
       <c r="F186" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -7134,13 +7134,13 @@
         </is>
       </c>
       <c r="H186" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>1.3131</v>
+        <v>1.5764</v>
       </c>
       <c r="J186" t="n">
-        <v>35.11</v>
+        <v>29.67</v>
       </c>
     </row>
     <row r="187">
@@ -7156,27 +7156,27 @@
         <v>64</v>
       </c>
       <c r="D187" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E187" t="n">
         <v>64</v>
       </c>
       <c r="F187" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H187" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>1.3234</v>
+        <v>1.3076</v>
       </c>
       <c r="J187" t="n">
-        <v>63.69</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="188">
@@ -7192,13 +7192,13 @@
         <v>64</v>
       </c>
       <c r="D188" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E188" t="n">
         <v>64</v>
       </c>
       <c r="F188" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -7206,13 +7206,13 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>1.3432</v>
+        <v>1.9993</v>
       </c>
       <c r="J188" t="n">
-        <v>32.49</v>
+        <v>22.98</v>
       </c>
     </row>
     <row r="189">
@@ -7228,27 +7228,27 @@
         <v>64</v>
       </c>
       <c r="D189" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E189" t="n">
         <v>64</v>
       </c>
       <c r="F189" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H189" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>1.3348</v>
+        <v>1.473</v>
       </c>
       <c r="J189" t="n">
-        <v>52.12</v>
+        <v>30.79</v>
       </c>
     </row>
     <row r="190">
@@ -7264,13 +7264,13 @@
         <v>64</v>
       </c>
       <c r="D190" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E190" t="n">
         <v>64</v>
       </c>
       <c r="F190" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -7278,13 +7278,13 @@
         </is>
       </c>
       <c r="H190" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>1.3951</v>
+        <v>1.3357</v>
       </c>
       <c r="J190" t="n">
-        <v>29.23</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="191">
@@ -7300,27 +7300,27 @@
         <v>64</v>
       </c>
       <c r="D191" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E191" t="n">
         <v>64</v>
       </c>
       <c r="F191" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H191" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>1.3599</v>
+        <v>1.5882</v>
       </c>
       <c r="J191" t="n">
-        <v>52.76</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="192">
@@ -7336,27 +7336,27 @@
         <v>64</v>
       </c>
       <c r="D192" t="n">
+        <v>3</v>
+      </c>
+      <c r="E192" t="n">
+        <v>64</v>
+      </c>
+      <c r="F192" t="n">
+        <v>16</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
         <v>5</v>
       </c>
-      <c r="E192" t="n">
-        <v>64</v>
-      </c>
-      <c r="F192" t="n">
-        <v>32</v>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="H192" t="n">
-        <v>6</v>
-      </c>
       <c r="I192" s="2" t="n">
-        <v>2.588</v>
+        <v>1.4204</v>
       </c>
       <c r="J192" t="n">
-        <v>21.04</v>
+        <v>379.65</v>
       </c>
     </row>
     <row r="193">
@@ -7372,27 +7372,27 @@
         <v>64</v>
       </c>
       <c r="D193" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E193" t="n">
         <v>64</v>
       </c>
       <c r="F193" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="H193" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>1.3341</v>
+        <v>1.3592</v>
       </c>
       <c r="J193" t="n">
-        <v>41.75</v>
+        <v>30.2</v>
       </c>
     </row>
   </sheetData>
